--- a/samples/survey_command11.xlsx
+++ b/samples/survey_command11.xlsx
@@ -591,27 +591,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>재난 초기대응 | 김한울 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
+          <t>재난 초기대응 | 장휘랑 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>재난 초기대응 | 김한울 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
+          <t>재난 초기대응 | 장휘랑 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>재난 초기대응 | 김한울 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
+          <t>재난 초기대응 | 장휘랑 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>재난 초기대응 | 김한울 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
+          <t>재난 초기대응 | 장휘랑 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>재난 초기대응 | 김한울 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
+          <t>재난 초기대응 | 장휘랑 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -701,7 +701,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -722,7 +721,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -743,7 +741,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -764,7 +761,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -885,7 +881,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -923,7 +918,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -944,7 +938,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1040,7 +1033,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1061,7 +1053,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
           <t>보통</t>
@@ -1199,7 +1190,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1220,7 +1210,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1266,7 +1255,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1287,7 +1275,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1333,7 +1320,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1421,7 +1407,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1442,7 +1427,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1463,7 +1447,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1484,7 +1467,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1505,7 +1487,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1593,7 +1574,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1639,7 +1619,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1660,7 +1639,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1681,7 +1659,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1702,7 +1679,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1723,7 +1699,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1769,7 +1744,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1807,7 +1781,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1878,7 +1851,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1899,7 +1871,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1945,7 +1916,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr">
         <is>
           <t>보통</t>
@@ -2083,7 +2053,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2129,7 +2098,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>보통</t>
@@ -2150,7 +2118,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2221,7 +2188,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2259,7 +2225,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2280,7 +2245,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2301,7 +2265,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2372,7 +2335,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2393,7 +2355,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2481,7 +2442,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2527,7 +2487,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2548,7 +2507,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2594,7 +2552,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2707,7 +2664,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2803,7 +2759,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>보통</t>
@@ -2824,7 +2779,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2845,7 +2799,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2933,7 +2886,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2954,7 +2906,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3050,7 +3001,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3071,7 +3021,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr">
         <is>
           <t>불만족</t>
@@ -3159,7 +3108,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3205,7 +3153,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3226,7 +3173,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3272,7 +3218,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
           <t>보통</t>
@@ -3343,7 +3288,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AV14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3431,7 +3375,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3477,7 +3420,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3498,7 +3440,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3519,7 +3460,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3565,7 +3505,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3603,7 +3542,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3624,7 +3562,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3670,7 +3607,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3691,7 +3627,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3787,7 +3722,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3850,7 +3784,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3871,7 +3804,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3892,7 +3824,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3913,7 +3844,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>보통</t>
@@ -3934,7 +3864,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4005,7 +3934,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4043,7 +3971,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4064,7 +3991,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4085,7 +4011,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4106,7 +4031,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4177,7 +4101,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4223,7 +4146,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4261,7 +4183,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4282,7 +4203,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4303,7 +4223,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4324,7 +4243,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4345,7 +4263,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4366,7 +4283,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4504,7 +4420,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4525,7 +4440,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4546,7 +4460,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4567,7 +4480,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4588,7 +4500,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4609,7 +4520,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4655,7 +4565,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4718,7 +4627,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4739,7 +4647,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4760,7 +4667,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4781,7 +4687,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4802,7 +4707,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4823,7 +4727,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr">
         <is>
           <t>보통</t>
@@ -4869,7 +4772,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4907,7 +4809,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4928,7 +4829,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4949,7 +4849,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4970,7 +4869,6 @@
           <t>불만족</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5016,7 +4914,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5037,7 +4934,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5083,7 +4979,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AV22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5171,7 +5066,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5192,7 +5086,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5213,7 +5106,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5234,7 +5126,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5397,7 +5288,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5418,7 +5308,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5439,7 +5328,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5460,7 +5348,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
           <t>보통</t>
@@ -5481,7 +5368,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5527,7 +5413,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5565,7 +5450,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5611,7 +5495,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5632,7 +5515,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5653,7 +5535,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5674,7 +5555,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5695,7 +5575,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5741,7 +5620,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AV25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5779,7 +5657,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5800,7 +5677,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5846,7 +5722,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5867,7 +5742,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6005,7 +5879,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6026,7 +5899,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6072,7 +5944,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6093,7 +5964,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6139,7 +6009,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6185,7 +6054,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AV27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6273,7 +6141,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6419,7 +6286,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AV28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6457,7 +6323,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6478,7 +6343,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6499,7 +6363,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6545,7 +6408,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6566,7 +6428,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6587,7 +6448,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6633,7 +6493,6 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AV29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6671,7 +6530,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6692,7 +6550,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6713,7 +6570,6 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6759,7 +6615,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6805,7 +6660,6 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr">
         <is>
           <t>만족</t>

--- a/samples/survey_command11.xlsx
+++ b/samples/survey_command11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV30"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,53 @@
           <t>현장지휘관 역량과정 11기 설문 결과(모의)</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -431,235 +478,240 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>소속 기관</t>
+          <t>소속</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>현재 계급</t>
+          <t>근무기간</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>보직</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>재난현장 지휘 | 문새론 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>재난현장 지휘 | 문새론 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>재난현장 지휘 | 문새론 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>재난현장 지휘 | 문새론 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>재난현장 지휘 | 문새론 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>상황판단 훈련 | 정바름 강사 | 태도: 교수님은 성실한 자세로 노력하며 강의(훈련)하였나요?</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>상황판단 훈련 | 정바름 강사 | 준비성: 훈련환경은 적절하고 장비는 충분했나요?</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>상황판단 훈련 | 정바름 강사 | 전문성: 교수님은 전문적이고 숙달된 자세로 훈련을 지도했나요?</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>상황판단 훈련 | 정바름 강사 | 적용성: 재난현장 및 실무에서 활용할 수 있는 훈련인가요?</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>상황판단 훈련 | 정바름 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>재난 브리핑 요령을 다룬 강의 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>재난 브리핑 요령을 다룬 강의 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>재난 브리핑 요령을 다룬 강의 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>재난 브리핑 요령을 다룬 강의 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>재난 브리핑 요령을 다룬 강의 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이나래 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이나래 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이나래 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이나래 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>스트레스 관리 | 이나래 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>리더십과 소통 | 이나래 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>리더십과 소통 | 이나래 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>리더십과 소통 | 이나래 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>리더십과 소통 | 이나래 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>리더십과 소통 | 이나래 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>공직가치 | 이나래 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>공직가치 | 이나래 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>공직가치 | 이나래 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>공직가치 | 이나래 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>공직가치 | 이나래 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>재난 초기대응 | 장휘랑 강사 | 태도: 강사는 성실하고 열의 있는 자세로 강의하였습니까?</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>재난 초기대응 | 장휘랑 강사 | 목표: 강의 내용은 교과목의 학습목표에 맞게 구성되었습니까?</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>재난 초기대응 | 장휘랑 강사 | 전달: 강사는 강의 내용을 이해하기 쉽게 전달하였습니까?</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>재난 초기대응 | 장휘랑 강사 | 효과: 강의 내용은 현장 직무 수행에 도움이 되겠습니까?</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>재난 초기대응 | 장휘랑 강사 | 의견: 이 교과목 또는 강사에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교재의 품질</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 강의실 및 교육기자재</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 편의시설</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>공통 | 교육시설환경 | 교직원의 친절도</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 구내식당 이용</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 음식의 간</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 메뉴의 다양성</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 청결도</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>공통 | 구내식당 | 친절도</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>공통 | 과정 운영 | 의견: 이번 과정 운영(일정·시설·안내 등)에 대한 의견을 자유롭게 적어 주세요(선택)</t>
         </is>
@@ -678,12 +730,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -693,7 +745,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -701,14 +753,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -718,14 +771,15 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -741,31 +795,33 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -773,49 +829,49 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>만족</t>
@@ -833,27 +889,27 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -863,7 +919,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -873,14 +929,20 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -890,17 +952,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -910,7 +972,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -918,11 +980,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -935,17 +998,18 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -960,14 +1024,14 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -975,49 +1039,49 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1025,19 +1089,20 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1045,22 +1110,23 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1070,17 +1136,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1090,15 +1156,20 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
@@ -1112,17 +1183,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1132,7 +1203,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1142,14 +1213,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1162,27 +1233,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1190,19 +1261,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1210,36 +1282,37 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1247,39 +1320,41 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1287,27 +1362,27 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -1317,9 +1392,15 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1329,22 +1410,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1354,19 +1435,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1379,19 +1460,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1407,11 +1488,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1419,7 +1501,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1427,14 +1509,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1447,11 +1530,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1459,7 +1543,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1467,14 +1551,15 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1487,11 +1572,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1504,12 +1590,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1519,20 +1605,25 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
         <is>
           <t>교육 운영 안내가 미리 와서 준비하기 좋았음</t>
         </is>
@@ -1546,22 +1637,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1571,47 +1662,48 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1619,19 +1711,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1639,11 +1732,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1656,14 +1750,15 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1679,19 +1774,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1699,19 +1795,20 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1726,12 +1823,12 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -1744,6 +1841,12 @@
           <t>만족</t>
         </is>
       </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1758,34 +1861,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1798,19 +1902,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -1823,39 +1927,40 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
           <t>만족</t>
@@ -1871,56 +1976,58 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
         <is>
           <t>보통</t>
@@ -1928,17 +2035,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1948,12 +2055,12 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -1962,6 +2069,11 @@
         </is>
       </c>
       <c r="AV8" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
         <is>
           <t>주차 공간이 부족했음</t>
         </is>
@@ -1975,44 +2087,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2020,32 +2132,32 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -2053,14 +2165,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2075,17 +2188,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2098,14 +2211,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2115,14 +2229,15 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2130,24 +2245,24 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN9" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2155,17 +2270,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2175,7 +2290,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2188,6 +2303,12 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2197,17 +2318,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2222,14 +2343,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2245,11 +2367,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2257,19 +2380,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2277,32 +2401,32 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2312,17 +2436,17 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -2332,14 +2456,15 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2347,19 +2472,20 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2367,32 +2493,32 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -2401,6 +2527,11 @@
         </is>
       </c>
       <c r="AV10" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
         <is>
           <t>주차 공간이 부족했음</t>
         </is>
@@ -2414,27 +2545,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2442,11 +2573,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2454,32 +2586,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2487,34 +2619,36 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2524,19 +2658,19 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -2549,42 +2683,43 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2594,17 +2729,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2623,6 +2758,11 @@
         </is>
       </c>
       <c r="AV11" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
         <is>
           <t>식당 대기 시간이 길었음</t>
         </is>
@@ -2636,47 +2776,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2686,42 +2827,42 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2736,22 +2877,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2759,51 +2900,54 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2831,20 +2975,25 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
         <is>
           <t>5일 과정이라 실습까지 충분히 해 볼 수 있었음</t>
         </is>
@@ -2858,17 +3007,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2886,59 +3035,61 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2948,44 +3099,44 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -2993,19 +3144,20 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3018,32 +3170,33 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr">
         <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -3053,12 +3206,12 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -3067,6 +3220,11 @@
         </is>
       </c>
       <c r="AV13" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
         <is>
           <t>주차 공간이 부족했음</t>
         </is>
@@ -3080,39 +3238,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3125,19 +3284,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3145,7 +3304,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -3153,11 +3312,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3165,19 +3325,20 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3195,17 +3356,17 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -3215,57 +3376,58 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -3280,14 +3442,20 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3297,89 +3465,90 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3397,14 +3566,14 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3412,39 +3581,41 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -3460,34 +3631,35 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -3497,7 +3669,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -3505,6 +3677,12 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3514,17 +3692,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3539,37 +3717,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3579,19 +3759,19 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3599,27 +3779,28 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -3627,36 +3808,37 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3674,17 +3856,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3694,17 +3876,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3714,14 +3896,20 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3731,52 +3919,52 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3784,14 +3972,15 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3804,54 +3993,57 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3864,36 +4056,37 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN17" t="inlineStr">
         <is>
           <t>만족</t>
@@ -3916,7 +4109,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3926,14 +4119,20 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3943,27 +4142,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3971,11 +4170,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>보통</t>
@@ -3983,7 +4183,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3991,19 +4191,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -4011,11 +4212,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4028,42 +4230,43 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -4078,34 +4281,35 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4128,12 +4332,12 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
@@ -4146,6 +4350,12 @@
           <t>매우 만족</t>
         </is>
       </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4160,17 +4370,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4180,14 +4390,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4195,7 +4406,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -4203,19 +4414,20 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -4223,14 +4435,15 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -4240,14 +4453,15 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4255,22 +4469,23 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -4280,52 +4495,53 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4340,12 +4556,12 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -4354,6 +4570,11 @@
         </is>
       </c>
       <c r="AV19" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
         <is>
           <t>5일 과정이라 실습까지 충분히 해 볼 수 있었음</t>
         </is>
@@ -4367,22 +4588,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4392,19 +4613,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4412,39 +4633,41 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4452,39 +4675,41 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4497,17 +4722,18 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -4517,22 +4743,23 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -4557,14 +4784,20 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4574,47 +4807,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -4624,14 +4857,15 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4647,11 +4881,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4667,11 +4902,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4679,7 +4915,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -4687,11 +4923,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4707,14 +4944,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4727,34 +4965,35 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -4764,14 +5003,20 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4781,22 +5026,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>소방장</t>
+          <t>10년 이상~20년 미만</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4806,22 +5051,23 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -4829,11 +5075,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -4849,11 +5096,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4866,39 +5114,40 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AD22" t="inlineStr">
         <is>
           <t>만족</t>
@@ -4911,22 +5160,23 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4934,29 +5184,30 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -4966,19 +5217,25 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4988,22 +5245,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>상황·통신</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5013,19 +5270,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>보통</t>
@@ -5033,27 +5290,27 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -5063,17 +5320,18 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -5083,17 +5341,18 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -5103,14 +5362,15 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5118,7 +5378,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -5126,44 +5386,45 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -5183,20 +5444,25 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
         <is>
           <t>식당 대기 시간이 길었음</t>
         </is>
@@ -5215,17 +5481,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>화재진압</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5240,14 +5506,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5255,24 +5521,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5288,31 +5554,33 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5320,42 +5588,44 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -5368,11 +5638,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5390,17 +5661,17 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
@@ -5410,9 +5681,15 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5422,17 +5699,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5447,39 +5724,40 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5495,11 +5773,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5507,7 +5786,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -5515,14 +5794,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -5532,22 +5812,23 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -5555,14 +5836,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -5572,14 +5854,15 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5587,12 +5870,12 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5607,19 +5890,25 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5629,59 +5918,61 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>예방·안전</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5699,34 +5990,35 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5742,11 +6034,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5764,17 +6057,17 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -5784,19 +6077,19 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
           <t>불만족</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
+      <c r="AM26" t="inlineStr">
         <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN26" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5814,12 +6107,12 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -5838,6 +6131,11 @@
         </is>
       </c>
       <c r="AV26" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
         <is>
           <t>과정 전체 일정 구성이 알찼음</t>
         </is>
@@ -5851,17 +6149,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>□□소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>소방사</t>
+          <t>5년 미만</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5871,19 +6169,20 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5899,14 +6198,15 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -5916,39 +6216,40 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>현장 사례를 들어 설명해 이해가 쉬웠음</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -5964,11 +6265,12 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -5976,24 +6278,24 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
           <t>사례가 조금 더 있으면 좋겠음</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AI27" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6009,19 +6311,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -6041,19 +6344,25 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6063,17 +6372,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>○○소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>소방교</t>
+          <t>5년 이상~10년 미만</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>행정</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6083,27 +6392,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -6118,17 +6427,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -6141,19 +6450,20 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -6163,14 +6473,14 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6178,27 +6488,27 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -6208,19 +6518,19 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
           <t>핵심만 짚어 주어 집중이 잘 됐음</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AI28" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6228,32 +6538,32 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
           <t>설명 속도가 빨라 따라가기 어려웠음</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -6263,12 +6573,12 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -6283,9 +6593,15 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6295,22 +6611,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>△△소방서</t>
+          <t>소방서</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6320,22 +6636,23 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -6343,19 +6660,20 @@
           <t>만족</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -6363,11 +6681,12 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6385,17 +6704,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
           <t>실습 시간이 부족했음</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -6405,14 +6724,15 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6420,19 +6740,20 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr">
         <is>
           <t>매우 만족</t>
@@ -6440,19 +6761,20 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6465,12 +6787,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -6480,19 +6802,25 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>만족</t>
-        </is>
-      </c>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6507,12 +6835,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>소방위</t>
+          <t>20년 이상</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>구급</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6527,22 +6855,23 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>매우 만족</t>
-        </is>
-      </c>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -6550,14 +6879,15 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -6570,36 +6900,37 @@
           <t>매우 만족</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>매우 만족</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
           <t>실습 장비가 충분해서 직접 해 볼 수 있었음</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6607,7 +6938,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -6615,19 +6946,20 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -6637,22 +6969,22 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
+          <t>만족</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
           <t>질문에 성실하게 답변해 주셔서 좋았음</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6660,11 +6992,12 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>만족</t>
-        </is>
-      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr">
         <is>
           <t>만족</t>
@@ -6682,7 +7015,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>만족</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -6697,15 +7030,20 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>매우 만족</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 만족</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
         <is>
           <t>주차 공간이 부족했음</t>
         </is>
